--- a/evaluation/results_metrics_evaluation.xlsx
+++ b/evaluation/results_metrics_evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waise\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{354DEF60-251E-4FAF-B789-95F13E3AA3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB642094-E2C7-4138-9B46-5356742D4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{11D98DA8-B1B9-4537-B518-867773BE73A0}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{11D98DA8-B1B9-4537-B518-867773BE73A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="398" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="394" uniqueCount="227">
   <si>
     <t>Tabellarische Auswertung der Ergebnisse und Metriken</t>
   </si>
@@ -247,9 +247,6 @@
   </si>
   <si>
     <t>Iterative</t>
-  </si>
-  <si>
-    <t>nicht separat</t>
   </si>
   <si>
     <t>sehr umfangreich</t>
@@ -1254,9 +1251,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1267,6 +1261,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="35" borderId="11" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1634,164 +1631,164 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
     </row>
     <row r="2" spans="1:4">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="30">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3">
+      <c r="C4" s="2">
         <v>2</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3">
+      <c r="C5" s="2">
         <v>2</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="3">
+      <c r="C6" s="2">
         <v>3</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="2" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="3" t="s">
+      <c r="D8" s="2" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="10" spans="1:4">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="2" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="30">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="5" t="s">
+      <c r="B12" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>41</v>
       </c>
     </row>
@@ -1823,573 +1820,573 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>46</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="30">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="3">
+      <c r="D2" s="2">
         <v>0</v>
       </c>
-      <c r="E2" s="3">
+      <c r="E2" s="2">
         <v>5</v>
       </c>
-      <c r="F2" s="3">
+      <c r="F2" s="2">
         <v>0</v>
       </c>
-      <c r="G2" s="3">
+      <c r="G2" s="2">
         <v>4</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="I2" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="J2" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="K2" s="5" t="s">
+      <c r="K2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="L2" s="2" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="30">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E3" s="2">
         <v>6</v>
       </c>
-      <c r="F3" s="3">
+      <c r="F3" s="2">
         <v>4</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3" s="2">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="H3" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="L3" s="2" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="30">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D4" s="2">
         <v>1</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="2">
         <v>10</v>
       </c>
-      <c r="F4" s="3">
+      <c r="F4" s="2">
         <v>8</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="2">
         <v>10</v>
       </c>
-      <c r="H4" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I4" s="3" t="s">
+      <c r="H4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="J4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="L4" s="2" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="30">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D5" s="2">
         <v>3</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="2">
+        <v>0</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0</v>
+      </c>
+      <c r="G5" s="2">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="K5" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="30">
+      <c r="A6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2">
+        <v>1</v>
+      </c>
+      <c r="E6" s="2">
+        <v>8</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="30">
+      <c r="A7" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="2">
+        <v>8</v>
+      </c>
+      <c r="F7" s="2">
+        <v>7</v>
+      </c>
+      <c r="G7" s="2">
+        <v>5</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="30">
+      <c r="A8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D8" s="2">
+        <v>3</v>
+      </c>
+      <c r="E8" s="2">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2">
+        <v>11</v>
+      </c>
+      <c r="G8" s="2">
+        <v>6</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="G5" s="3">
-        <v>15</v>
-      </c>
-      <c r="H5" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I5" s="3" t="s">
+      <c r="K8" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="30">
+      <c r="A9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="2">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2">
+        <v>7</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0</v>
+      </c>
+      <c r="G9" s="2">
+        <v>5</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K5" s="4" t="s">
+      <c r="I9" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="30">
+      <c r="A10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D10" s="2">
+        <v>1</v>
+      </c>
+      <c r="E10" s="2">
+        <v>14</v>
+      </c>
+      <c r="F10" s="2">
+        <v>5</v>
+      </c>
+      <c r="G10" s="2">
+        <v>13</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="2">
+        <v>16</v>
+      </c>
+      <c r="F11" s="2">
+        <v>13</v>
+      </c>
+      <c r="G11" s="2">
+        <v>13</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="L5" s="3" t="s">
+      <c r="L11" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D12" s="2">
+        <v>3</v>
+      </c>
+      <c r="E12" s="2">
+        <v>0</v>
+      </c>
+      <c r="F12" s="2">
+        <v>0</v>
+      </c>
+      <c r="G12" s="2">
+        <v>39</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="30">
+      <c r="A13" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="30">
-      <c r="A6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D6" s="3">
+      <c r="D13" s="2">
         <v>1</v>
       </c>
-      <c r="E6" s="3">
+      <c r="E13" s="2">
         <v>8</v>
       </c>
-      <c r="F6" s="3">
+      <c r="F13" s="2">
+        <v>4</v>
+      </c>
+      <c r="G13" s="2">
+        <v>6</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="30">
+      <c r="A14" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="2">
+        <v>12</v>
+      </c>
+      <c r="F14" s="2">
+        <v>8</v>
+      </c>
+      <c r="G14" s="2">
+        <v>9</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="30">
+      <c r="A15" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D15" s="2">
         <v>3</v>
       </c>
-      <c r="G6" s="3">
-        <v>5</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I6" s="3" t="s">
+      <c r="E15" s="2">
+        <v>16</v>
+      </c>
+      <c r="F15" s="2">
+        <v>7</v>
+      </c>
+      <c r="G15" s="2">
+        <v>9</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="30">
-      <c r="A7" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D7" s="3">
-        <v>1</v>
-      </c>
-      <c r="E7" s="3">
-        <v>8</v>
-      </c>
-      <c r="F7" s="3">
-        <v>7</v>
-      </c>
-      <c r="G7" s="3">
-        <v>5</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="30">
-      <c r="A8" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="3">
-        <v>3</v>
-      </c>
-      <c r="E8" s="3">
-        <v>12</v>
-      </c>
-      <c r="F8" s="3">
-        <v>11</v>
-      </c>
-      <c r="G8" s="3">
-        <v>5</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K8" s="5" t="s">
-        <v>81</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="30">
-      <c r="A9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="D9" s="3">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3">
-        <v>7</v>
-      </c>
-      <c r="F9" s="3">
-        <v>0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>5</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="K9" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="30">
-      <c r="A10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="3">
-        <v>1</v>
-      </c>
-      <c r="E10" s="3">
-        <v>14</v>
-      </c>
-      <c r="F10" s="3">
-        <v>5</v>
-      </c>
-      <c r="G10" s="3">
-        <v>13</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
-      <c r="A11" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D11" s="3">
-        <v>1</v>
-      </c>
-      <c r="E11" s="3">
-        <v>16</v>
-      </c>
-      <c r="F11" s="3">
-        <v>13</v>
-      </c>
-      <c r="G11" s="3">
-        <v>13</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="30">
-      <c r="A12" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="3">
-        <v>3</v>
-      </c>
-      <c r="E12" s="3" t="s">
+      <c r="J15" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G12" s="3">
-        <v>39</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K12" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="30">
-      <c r="A13" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D13" s="3">
-        <v>1</v>
-      </c>
-      <c r="E13" s="3">
-        <v>8</v>
-      </c>
-      <c r="F13" s="3">
-        <v>4</v>
-      </c>
-      <c r="G13" s="3">
-        <v>6</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="30">
-      <c r="A14" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="D14" s="3">
-        <v>1</v>
-      </c>
-      <c r="E14" s="3">
-        <v>12</v>
-      </c>
-      <c r="F14" s="3">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3">
-        <v>6</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="L14" s="3" t="s">
+      <c r="K15" s="4" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" ht="30">
-      <c r="A15" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="D15" s="3">
-        <v>3</v>
-      </c>
-      <c r="E15" s="3">
-        <v>16</v>
-      </c>
-      <c r="F15" s="3">
-        <v>7</v>
-      </c>
-      <c r="G15" s="3">
-        <v>7</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="K15" s="5" t="s">
+      <c r="L15" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>93</v>
       </c>
     </row>
   </sheetData>
@@ -2408,139 +2405,139 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:5" ht="30">
+      <c r="A2" s="2" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" ht="30">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="D2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="30">
+      <c r="A3" s="2" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" ht="30">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="30">
+      <c r="A4" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="30">
-      <c r="A4" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="30">
+      <c r="A5" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="30">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="E6" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="30">
+      <c r="A7" s="2" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="30">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="D7" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="E7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="30">
+      <c r="A8" s="2" t="s">
         <v>124</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="30">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>128</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>129</v>
       </c>
     </row>
   </sheetData>
@@ -2561,325 +2558,325 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
+      <c r="A2" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="3" t="s">
+      <c r="B2" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E2" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F2" s="4" t="s">
+      <c r="G2" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="G2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="2" t="s">
         <v>134</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="3" t="s">
+      <c r="G4" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="G4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:7" ht="30">
+      <c r="A5" s="2" t="s">
         <v>138</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="30">
-      <c r="A5" s="3" t="s">
+      <c r="B5" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="G5" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="G5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:7" ht="30">
+      <c r="A6" s="2" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="30">
-      <c r="A6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="5" t="s">
+      <c r="D6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F6" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:7" ht="30">
+      <c r="A7" s="2" t="s">
         <v>144</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="30">
-      <c r="A7" s="3" t="s">
+      <c r="B7" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="B7" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F7" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="2" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="3" t="s">
+      <c r="B8" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="B8" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C8" s="3" t="s">
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C9" s="3" t="s">
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F9" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="G10" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F10" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C11" s="3" t="s">
+      <c r="G11" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D11" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="30">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C12" s="3" t="s">
+    </row>
+    <row r="13" spans="1:7" ht="30">
+      <c r="A13" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D12" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="30">
-      <c r="A13" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="B13" s="3" t="s">
+      <c r="D13" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="F13" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="G13" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D13" s="5" t="s">
-        <v>86</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="F13" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="G13" s="3" t="s">
+      <c r="D14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="F14" s="4" t="s">
+      <c r="G14" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>164</v>
       </c>
     </row>
   </sheetData>
@@ -2898,91 +2895,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>165</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="C1" s="2" t="s">
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="C2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="2" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C3" s="3" t="s">
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="2" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="3" t="s">
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="3" t="s">
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="3" t="s">
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="3" t="s">
+    </row>
+    <row r="8" spans="1:3" ht="30">
+      <c r="A8" s="4" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="30">
-      <c r="A8" s="5" t="s">
+      <c r="B8" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>182</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -3001,373 +2998,373 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="21">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="2" t="s">
+      <c r="B2" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>185</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="3" t="s">
+      <c r="B3" s="2">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2">
+        <v>2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>2</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="3">
+      <c r="B4" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="2">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2">
+        <v>3</v>
+      </c>
+      <c r="E4" s="2">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="B5" s="2">
+        <v>0</v>
+      </c>
+      <c r="C5" s="2">
+        <v>6</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6</v>
+      </c>
+      <c r="E5" s="2">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="B6" s="2">
         <v>2</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C6" s="2">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0</v>
+      </c>
+      <c r="E6" s="2">
         <v>2</v>
       </c>
-      <c r="D3" s="3">
+      <c r="F6" s="2" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>10</v>
+      </c>
+      <c r="D7" s="2">
+        <v>10</v>
+      </c>
+      <c r="E7" s="2">
+        <v>20</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="B8" s="2">
+        <v>12</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E8" s="2">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="B9" s="2">
+        <v>9</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E9" s="2">
+        <v>9</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30">
+      <c r="A10" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C10" s="2">
+        <v>46</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E10" s="2">
+        <v>46</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D11" s="2">
+        <v>64</v>
+      </c>
+      <c r="E11" s="2">
+        <v>64</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="30">
+      <c r="A12" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C12" s="2">
+        <v>30</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E12" s="2">
+        <v>30</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30">
+      <c r="A13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D13" s="2">
+        <v>42</v>
+      </c>
+      <c r="E13" s="2">
+        <v>42</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30">
+      <c r="A14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C14" s="2">
+        <v>96</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="E14" s="2">
+        <v>96</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="30">
+      <c r="A15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="D15" s="2">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2">
+        <v>40</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="B16" s="2">
+        <v>0</v>
+      </c>
+      <c r="C16" s="2">
+        <v>4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>5</v>
+      </c>
+      <c r="E16" s="2">
+        <v>9</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30">
+      <c r="A17" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="B17" s="2">
+        <v>0</v>
+      </c>
+      <c r="C17" s="2">
         <v>2</v>
       </c>
-      <c r="E3" s="3">
+      <c r="D17" s="2">
         <v>2</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C4" s="3">
-        <v>3</v>
-      </c>
-      <c r="D4" s="3">
-        <v>3</v>
-      </c>
-      <c r="E4" s="3">
-        <v>3</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="B5" s="3">
-        <v>0</v>
-      </c>
-      <c r="C5" s="3">
-        <v>6</v>
-      </c>
-      <c r="D5" s="3">
-        <v>6</v>
-      </c>
-      <c r="E5" s="3">
-        <v>12</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="B6" s="3">
-        <v>2</v>
-      </c>
-      <c r="C6" s="3">
-        <v>0</v>
-      </c>
-      <c r="D6" s="3">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3">
-        <v>2</v>
-      </c>
-      <c r="F6" s="3" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="B7" s="3">
-        <v>0</v>
-      </c>
-      <c r="C7" s="3">
-        <v>10</v>
-      </c>
-      <c r="D7" s="3">
-        <v>10</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="E17" s="2">
+        <v>4</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30">
+      <c r="A18" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D18" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="F7" s="3" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B8" s="3">
-        <v>12</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E8" s="3">
-        <v>12</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="B9" s="3">
-        <v>9</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E9" s="3">
-        <v>9</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="30">
-      <c r="A10" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E10" s="3">
-        <v>46</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D11" s="3">
-        <v>64</v>
-      </c>
-      <c r="E11" s="3">
-        <v>64</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="30">
-      <c r="A12" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C12" s="3">
-        <v>30</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E12" s="3">
-        <v>30</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="30">
-      <c r="A13" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D13" s="3">
-        <v>40</v>
-      </c>
-      <c r="E13" s="3">
-        <v>40</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="30">
-      <c r="A14" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C14" s="3">
-        <v>96</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E14" s="3">
-        <v>96</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" ht="30">
-      <c r="A15" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="D15" s="3">
-        <v>34</v>
-      </c>
-      <c r="E15" s="3">
-        <v>34</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="B16" s="3">
-        <v>0</v>
-      </c>
-      <c r="C16" s="3">
-        <v>4</v>
-      </c>
-      <c r="D16" s="3">
-        <v>5</v>
-      </c>
-      <c r="E16" s="3">
-        <v>9</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" ht="30">
-      <c r="A17" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="B17" s="3">
-        <v>0</v>
-      </c>
-      <c r="C17" s="3">
-        <v>2</v>
-      </c>
-      <c r="D17" s="3">
-        <v>2</v>
-      </c>
-      <c r="E17" s="3">
-        <v>4</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" ht="30">
-      <c r="A18" s="5" t="s">
-        <v>217</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>218</v>
-      </c>
-      <c r="C18" s="5" t="s">
+      <c r="E18" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="D18" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="5" t="s">
+      <c r="F18" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="F18" s="5" t="s">
+    </row>
+    <row r="19" spans="1:6" ht="30">
+      <c r="A19" s="3" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="19" spans="1:6" ht="30">
-      <c r="A19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="D19" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="E19" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>226</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>227</v>
       </c>
     </row>
   </sheetData>

--- a/evaluation/results_metrics_evaluation.xlsx
+++ b/evaluation/results_metrics_evaluation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\waise\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB642094-E2C7-4138-9B46-5356742D4738}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C94F15C-52C6-43C9-95A8-95C4B13264EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{11D98DA8-B1B9-4537-B518-867773BE73A0}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="16305" firstSheet="3" activeTab="5" xr2:uid="{11D98DA8-B1B9-4537-B518-867773BE73A0}"/>
   </bookViews>
   <sheets>
     <sheet name="Uebersicht" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,18 @@
     <sheet name="Legende" sheetId="5" r:id="rId5"/>
     <sheet name="Kennzahlen" sheetId="6" r:id="rId6"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -453,9 +464,6 @@
     <t>Fälligkeitsdatum</t>
   </si>
   <si>
-    <t>Nur Student</t>
-  </si>
-  <si>
     <t>Für To-do als Erweiterung, für Student Task Manager zentral</t>
   </si>
   <si>
@@ -504,9 +512,6 @@
     <t>Cloud/Sync/Offline</t>
   </si>
   <si>
-    <t>vor allem Student</t>
-  </si>
-  <si>
     <t>Zu prüfen</t>
   </si>
   <si>
@@ -706,6 +711,12 @@
   </si>
   <si>
     <t>Die Metriken zeigen, dass KI deutlich mehr Struktur und Zusatzaspekte liefert als die manuelle Baseline.</t>
+  </si>
+  <si>
+    <t>Nur StudentTaskM.</t>
+  </si>
+  <si>
+    <t>vor allem Student Task Manager</t>
   </si>
 </sst>
 </file>
@@ -1991,7 +2002,7 @@
         <v>0</v>
       </c>
       <c r="G5" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>63</v>
@@ -2680,7 +2691,7 @@
         <v>131</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>142</v>
+        <v>225</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>63</v>
@@ -2692,12 +2703,12 @@
         <v>139</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="30">
       <c r="A7" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>82</v>
@@ -2715,12 +2726,12 @@
         <v>139</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>82</v>
@@ -2738,12 +2749,12 @@
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>82</v>
@@ -2761,12 +2772,12 @@
         <v>139</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>82</v>
@@ -2781,15 +2792,15 @@
         <v>63</v>
       </c>
       <c r="F10" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>131</v>
@@ -2804,15 +2815,15 @@
         <v>63</v>
       </c>
       <c r="F11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>154</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="30">
       <c r="A12" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>131</v>
@@ -2827,18 +2838,18 @@
         <v>63</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="30">
       <c r="A13" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>159</v>
+        <v>226</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>57</v>
@@ -2850,10 +2861,10 @@
         <v>63</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -2873,10 +2884,10 @@
         <v>63</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
   </sheetData>
@@ -2896,13 +2907,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>164</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -2910,10 +2921,10 @@
         <v>46</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -2921,21 +2932,21 @@
         <v>47</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -2943,10 +2954,10 @@
         <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -2954,10 +2965,10 @@
         <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -2965,21 +2976,21 @@
         <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="30">
       <c r="A8" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>180</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="4" t="s">
-        <v>182</v>
       </c>
     </row>
   </sheetData>
@@ -2999,7 +3010,7 @@
   <sheetData>
     <row r="1" spans="1:6" ht="21">
       <c r="A1" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="B1" s="5"/>
       <c r="C1" s="5"/>
@@ -3009,7 +3020,7 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>56</v>
@@ -3021,15 +3032,15 @@
         <v>76</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="2" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B3" s="2">
         <v>2</v>
@@ -3049,10 +3060,10 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C4" s="2">
         <v>3</v>
@@ -3064,12 +3075,12 @@
         <v>3</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B5" s="2">
         <v>0</v>
@@ -3081,15 +3092,16 @@
         <v>6</v>
       </c>
       <c r="E5" s="2">
+        <f>SUM(C5:D5)</f>
         <v>12</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B6" s="2">
         <v>2</v>
@@ -3101,15 +3113,16 @@
         <v>0</v>
       </c>
       <c r="E6" s="2">
+        <f>SUM(B6:D6)</f>
         <v>2</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B7" s="2">
         <v>0</v>
@@ -3121,175 +3134,192 @@
         <v>10</v>
       </c>
       <c r="E7" s="2">
+        <f t="shared" ref="E7:E17" si="0">SUM(B7:D7)</f>
         <v>20</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="2" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B8" s="2">
+        <f>SUM(Metriken!E2,Metriken!E9)</f>
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E8" s="2">
+        <f t="shared" si="0"/>
         <v>12</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B9" s="2">
+        <f>SUM(Metriken!G2,Metriken!G9)</f>
         <v>9</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E9" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
     </row>
     <row r="10" spans="1:6" ht="30">
       <c r="A10" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C10" s="2">
+        <f>SUM(Metriken!E3:E5,Metriken!E10:E12)</f>
         <v>46</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E10" s="2">
+        <f t="shared" si="0"/>
         <v>46</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D11" s="2">
+        <f>SUM(Metriken!E6:E8,Metriken!E13:E15)</f>
         <v>64</v>
       </c>
       <c r="E11" s="2">
+        <f t="shared" si="0"/>
         <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
     </row>
     <row r="12" spans="1:6" ht="30">
       <c r="A12" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C12" s="2">
+        <f>SUM(Metriken!F3:F5,Metriken!F10:F12)</f>
         <v>30</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E12" s="2">
+        <f t="shared" si="0"/>
         <v>30</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
     </row>
     <row r="13" spans="1:6" ht="30">
       <c r="A13" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D13" s="2">
-        <v>42</v>
+        <f>SUM(Metriken!F6:F8,Metriken!F13:F15)</f>
+        <v>40</v>
       </c>
       <c r="E13" s="2">
-        <v>42</v>
+        <f t="shared" si="0"/>
+        <v>40</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="30">
       <c r="A14" s="2" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C14" s="2">
-        <v>96</v>
+        <f>SUM(Metriken!G3:G5,Metriken!G10:G12)</f>
+        <v>98</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E14" s="2">
-        <v>96</v>
+        <f t="shared" si="0"/>
+        <v>98</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="15" spans="1:6" ht="30">
       <c r="A15" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="D15" s="2">
+        <f>SUM(Metriken!G6:G8,Metriken!G13:G15)</f>
         <v>40</v>
       </c>
       <c r="E15" s="2">
+        <f t="shared" si="0"/>
         <v>40</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="2" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B16" s="2">
         <v>0</v>
@@ -3301,15 +3331,16 @@
         <v>5</v>
       </c>
       <c r="E16" s="2">
+        <f t="shared" si="0"/>
         <v>9</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="30">
       <c r="A17" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B17" s="2">
         <v>0</v>
@@ -3321,50 +3352,51 @@
         <v>2</v>
       </c>
       <c r="E17" s="2">
+        <f t="shared" si="0"/>
         <v>4</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="30">
       <c r="A18" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="C18" s="4" t="s">
         <v>216</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>217</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>218</v>
       </c>
       <c r="D18" s="4" t="s">
         <v>20</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="30">
       <c r="A19" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C19" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="D19" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="E19" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="F19" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
   </sheetData>
